--- a/uploads/lab_rooms.xlsx
+++ b/uploads/lab_rooms.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E06DB9-97E8-438E-B565-3D39F5057F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D96B92E9-F35B-4AB9-8DA9-F1BDF1FE6C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2268" yWindow="2268" windowWidth="17280" windowHeight="8880" xr2:uid="{C81C6726-5086-4F86-A491-46F0D6D31795}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C81C6726-5086-4F86-A491-46F0D6D31795}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="85">
   <si>
     <t>class</t>
   </si>
@@ -191,34 +191,16 @@
     <t>rooms</t>
   </si>
   <si>
-    <t>A101</t>
-  </si>
-  <si>
     <t xml:space="preserve">PROJ[TE LAB/GT LAB] </t>
   </si>
   <si>
-    <t>A102</t>
-  </si>
-  <si>
-    <t>A103</t>
-  </si>
-  <si>
     <t xml:space="preserve">Project </t>
   </si>
   <si>
-    <t>A104</t>
-  </si>
-  <si>
-    <t>A105</t>
-  </si>
-  <si>
     <t>Proj II</t>
   </si>
   <si>
     <t>CP/PHY LAB</t>
-  </si>
-  <si>
-    <t>A101,A102</t>
   </si>
   <si>
     <t>IT W/S / PHL</t>
@@ -232,67 +214,22 @@
  </t>
   </si>
   <si>
-    <t>A103,A102</t>
-  </si>
-  <si>
-    <t>A103,A101</t>
-  </si>
-  <si>
-    <t>A101,102</t>
-  </si>
-  <si>
-    <t>A103,102</t>
-  </si>
-  <si>
     <t>W/S EE/WS EC</t>
   </si>
   <si>
-    <t>A104,A105</t>
-  </si>
-  <si>
-    <t>A106,A105</t>
-  </si>
-  <si>
-    <t>A106,A104</t>
-  </si>
-  <si>
-    <t>A106</t>
-  </si>
-  <si>
     <t>A107</t>
   </si>
   <si>
     <t>PC LAB/CHEMISTRY LAB</t>
   </si>
   <si>
-    <t>A106,A101</t>
-  </si>
-  <si>
-    <t>A103,A106</t>
-  </si>
-  <si>
     <t>Chem Lab/ C Lab</t>
   </si>
   <si>
-    <t>A101,A103</t>
-  </si>
-  <si>
-    <t>A106,A103</t>
-  </si>
-  <si>
-    <t>A105,A101</t>
-  </si>
-  <si>
     <t>A108,A107</t>
   </si>
   <si>
-    <t>A109</t>
-  </si>
-  <si>
     <t xml:space="preserve">DC Machines Lab/Power Electronics Lab </t>
-  </si>
-  <si>
-    <t>A201,A202</t>
   </si>
   <si>
     <t xml:space="preserve">LIC LAB/MC LAB
@@ -302,28 +239,61 @@
     <t>A203,A204</t>
   </si>
   <si>
-    <t>A105,A205</t>
-  </si>
-  <si>
-    <t>A206,A107</t>
-  </si>
-  <si>
     <t>A206,A207</t>
   </si>
   <si>
     <t>A207,A107</t>
   </si>
   <si>
-    <t>A208</t>
-  </si>
-  <si>
-    <t>A209</t>
-  </si>
-  <si>
     <t>CP LAB / IT W/S</t>
   </si>
   <si>
     <t>W/S EE/W/S EC</t>
+  </si>
+  <si>
+    <t>A501</t>
+  </si>
+  <si>
+    <t>A507</t>
+  </si>
+  <si>
+    <t>A507,102</t>
+  </si>
+  <si>
+    <t>A507,A501</t>
+  </si>
+  <si>
+    <t>A501,A507</t>
+  </si>
+  <si>
+    <t>A507,A507</t>
+  </si>
+  <si>
+    <t>A201,A509</t>
+  </si>
+  <si>
+    <t>D101</t>
+  </si>
+  <si>
+    <t>A505</t>
+  </si>
+  <si>
+    <t>A401B,A402B</t>
+  </si>
+  <si>
+    <t>A401B,A</t>
+  </si>
+  <si>
+    <t>A401,A205</t>
+  </si>
+  <si>
+    <t>A401,A507</t>
+  </si>
+  <si>
+    <t>A401,102</t>
+  </si>
+  <si>
+    <t>A,A507</t>
   </si>
 </sst>
 </file>
@@ -717,6 +687,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="38.109375" customWidth="1"/>
+    <col min="3" max="3" width="18.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -738,7 +709,7 @@
         <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -746,10 +717,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -760,7 +731,7 @@
         <v>43</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -768,10 +739,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -779,10 +750,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -793,7 +764,7 @@
         <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -804,7 +775,7 @@
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -812,10 +783,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -826,7 +797,7 @@
         <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -837,7 +808,7 @@
         <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -845,10 +816,10 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -859,7 +830,7 @@
         <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -867,10 +838,10 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -878,10 +849,10 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -892,7 +863,7 @@
         <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -900,10 +871,10 @@
         <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -914,7 +885,7 @@
         <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -922,10 +893,10 @@
         <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -936,7 +907,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
@@ -944,10 +915,10 @@
         <v>10</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C21" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
@@ -955,10 +926,10 @@
         <v>10</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -969,7 +940,7 @@
         <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -980,7 +951,7 @@
         <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -988,10 +959,10 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C25" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -1002,7 +973,7 @@
         <v>29</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -1013,7 +984,7 @@
         <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -1021,10 +992,10 @@
         <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C28" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -1035,7 +1006,7 @@
         <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1057,7 +1028,7 @@
         <v>32</v>
       </c>
       <c r="C31" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1068,7 +1039,7 @@
         <v>31</v>
       </c>
       <c r="C32" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -1079,7 +1050,7 @@
         <v>30</v>
       </c>
       <c r="C33" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -1087,10 +1058,10 @@
         <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="C34" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
@@ -1098,10 +1069,10 @@
         <v>18</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C35" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
@@ -1112,7 +1083,7 @@
         <v>41</v>
       </c>
       <c r="C36" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -1123,7 +1094,7 @@
         <v>33</v>
       </c>
       <c r="C37" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -1134,7 +1105,7 @@
         <v>33</v>
       </c>
       <c r="C38" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -1145,7 +1116,7 @@
         <v>38</v>
       </c>
       <c r="C39" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
@@ -1156,7 +1127,7 @@
         <v>35</v>
       </c>
       <c r="C40" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
@@ -1167,7 +1138,7 @@
         <v>34</v>
       </c>
       <c r="C41" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
@@ -1178,7 +1149,7 @@
         <v>37</v>
       </c>
       <c r="C42" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
@@ -1189,7 +1160,7 @@
         <v>36</v>
       </c>
       <c r="C43" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="56" spans="2:2" ht="18" x14ac:dyDescent="0.35">

--- a/uploads/lab_rooms.xlsx
+++ b/uploads/lab_rooms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D96B92E9-F35B-4AB9-8DA9-F1BDF1FE6C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC475C51-BFBA-495C-935E-0EDD1EBE3AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C81C6726-5086-4F86-A491-46F0D6D31795}"/>
   </bookViews>
@@ -281,9 +281,6 @@
     <t>A401B,A402B</t>
   </si>
   <si>
-    <t>A401B,A</t>
-  </si>
-  <si>
     <t>A401,A205</t>
   </si>
   <si>
@@ -294,6 +291,9 @@
   </si>
   <si>
     <t>A,A507</t>
+  </si>
+  <si>
+    <t>A401B,A507</t>
   </si>
 </sst>
 </file>
@@ -786,7 +786,7 @@
         <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -797,7 +797,7 @@
         <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -819,7 +819,7 @@
         <v>54</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -852,7 +852,7 @@
         <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -863,7 +863,7 @@
         <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -1006,7 +1006,7 @@
         <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1017,7 +1017,7 @@
         <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1083,7 +1083,7 @@
         <v>41</v>
       </c>
       <c r="C36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
